--- a/docs/oc-mensuales/suministro-de-combustibles/dic-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16372.63</v>
+        <v>16161.01</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6439.9</v>
+        <v>6356.66</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>16372.63</v>
+        <v>16161.01</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2292.17</v>
+        <v>2262.54</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>36893</v>
+        <v>36416.14</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2510.47</v>
+        <v>2478.02</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10915.09</v>
+        <v>10774</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>32231.16</v>
+        <v>31814.56</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>17464.14</v>
+        <v>17238.41</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6760.23</v>
+        <v>6672.85</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2292.17</v>
+        <v>2262.54</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5348.39</v>
+        <v>5279.26</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8732.07</v>
+        <v>8619.200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6549.05</v>
+        <v>6464.4</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>37951.76</v>
+        <v>37461.21</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2292.17</v>
+        <v>2262.54</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3820.28</v>
+        <v>3770.9</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3492.83</v>
+        <v>3447.68</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2401.32</v>
+        <v>2370.28</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4366.04</v>
+        <v>4309.6</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4911.79</v>
+        <v>4848.3</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3274.53</v>
+        <v>3232.2</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4366.04</v>
+        <v>4309.6</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5457.54</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10915.09</v>
+        <v>10774</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3274.53</v>
+        <v>3232.2</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5457.54</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3274.53</v>
+        <v>3232.2</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9823.58</v>
+        <v>9696.6</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5457.54</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9823.58</v>
+        <v>9696.6</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2401.32</v>
+        <v>2370.82</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2433.32</v>
+        <v>2402.41</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2401.32</v>
+        <v>2370.82</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>43660.35</v>
+        <v>43105.77</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>17464.14</v>
+        <v>17242.31</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3383.68</v>
+        <v>3340.7</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4366.04</v>
+        <v>4310.58</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5457.54</v>
+        <v>5388.22</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7080.04</v>
+        <v>6990.11</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>61124.49</v>
+        <v>60348.08</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3486.71</v>
+        <v>3442.42</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>27375.04</v>
+        <v>27027.32</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4801.55</v>
+        <v>4740.56</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7640.56</v>
+        <v>7543.51</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5457.54</v>
+        <v>5388.22</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>11482.67</v>
+        <v>11336.82</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10915.09</v>
+        <v>10776.44</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2292.17</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2728.77</v>
+        <v>2694.11</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5239.24</v>
+        <v>5172.69</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>6549.05</v>
+        <v>6465.87</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>27287.72</v>
+        <v>26941.11</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6549.05</v>
+        <v>6465.87</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3274.53</v>
+        <v>3232.93</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2292.17</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5130.09</v>
+        <v>5064.93</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>32745.26</v>
+        <v>32329.33</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>37111.3</v>
+        <v>36639.91</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4366.04</v>
+        <v>4310.58</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>16372.63</v>
+        <v>16164.66</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2292.17</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2292.17</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2277.98</v>
+        <v>2249.04</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2728.77</v>
+        <v>2694.11</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2300.89</v>
+        <v>2271.66</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>8732.07</v>
+        <v>8621.15</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>36019.79</v>
+        <v>35562.26</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>16372.63</v>
+        <v>16164.66</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3274.53</v>
+        <v>3241.95</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>16270.84</v>
+        <v>16108.96</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>16372.63</v>
+        <v>16209.73</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5457.54</v>
+        <v>5403.24</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>6439.9</v>
+        <v>6375.83</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>12825.23</v>
+        <v>12697.62</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3929.43</v>
+        <v>3890.34</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3885.62</v>
+        <v>3846.96</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10915.09</v>
+        <v>10806.49</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4366.04</v>
+        <v>4322.6</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>15281.12</v>
+        <v>15129.08</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2401.32</v>
+        <v>2377.43</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>10915.09</v>
+        <v>10806.49</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5743.97</v>
+        <v>5686.82</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2277.17</v>
+        <v>2254.51</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4366.04</v>
+        <v>4322.6</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4366.04</v>
+        <v>4322.6</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>9059.52</v>
+        <v>8969.389999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2292.17</v>
+        <v>2269.36</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4366.04</v>
+        <v>4322.6</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>9823.58</v>
+        <v>9725.84</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>6549.05</v>
+        <v>6483.89</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>56758.46</v>
+        <v>56193.74</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5457.54</v>
+        <v>5403.24</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2678.03</v>
+        <v>2651.38</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2292.17</v>
+        <v>2269.36</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4256.88</v>
+        <v>4214.53</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>21830.18</v>
+        <v>21612.98</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2292.17</v>
+        <v>2269.36</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3820.28</v>
+        <v>3782.27</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>9145.639999999999</v>
+        <v>9054.639999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2727.68</v>
+        <v>2700.54</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2277.17</v>
+        <v>2254.51</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4911.79</v>
+        <v>4862.92</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10915.09</v>
+        <v>10806.49</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6549.05</v>
+        <v>6483.89</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9349.860000000001</v>
+        <v>9256.84</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5457.54</v>
+        <v>5403.24</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3274.53</v>
+        <v>3241.95</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5457.54</v>
+        <v>5403.24</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>10915.08</v>
+        <v>10806.48</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3492.83</v>
+        <v>3480.3</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5199.4</v>
+        <v>5180.76</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2817.17</v>
+        <v>2807.07</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>13098.11</v>
+        <v>13051.14</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>6549.05</v>
+        <v>6525.57</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>7640.56</v>
+        <v>7613.16</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5457.54</v>
+        <v>5437.97</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2442.8</v>
+        <v>2434.04</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2401.32</v>
+        <v>2392.71</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>8732.07</v>
+        <v>8700.76</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5832.04</v>
+        <v>5811.12</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>7640.56</v>
+        <v>7613.16</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>7694.81</v>
+        <v>7667.22</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4946.66</v>
+        <v>4928.93</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2277.17</v>
+        <v>2269.01</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3274.53</v>
+        <v>3262.78</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>10915.09</v>
+        <v>10875.95</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>33836.77</v>
+        <v>33715.44</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3274.53</v>
+        <v>3262.78</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>24407.77</v>
+        <v>24320.25</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3274.53</v>
+        <v>3262.78</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>10915.09</v>
+        <v>10875.95</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2281.25</v>
+        <v>2273.07</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2401.32</v>
+        <v>2392.71</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6549.05</v>
+        <v>6525.57</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4147.73</v>
+        <v>4132.86</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3274.53</v>
+        <v>3262.78</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2837.92</v>
+        <v>2827.75</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2277.17</v>
+        <v>2269.01</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8186.32</v>
+        <v>8156.96</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2728.77</v>
+        <v>2718.99</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3615.43</v>
+        <v>3602.46</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>10915.09</v>
+        <v>10875.95</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3274.53</v>
+        <v>3262.78</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5909.14</v>
+        <v>5887.96</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>10696.79</v>
+        <v>10658.43</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>4366.04</v>
+        <v>4350.38</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2277.17</v>
+        <v>2269.01</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>6003.3</v>
+        <v>5981.77</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>14899.1</v>
+        <v>14845.67</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4366.04</v>
+        <v>4350.38</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2284.84</v>
+        <v>2276.65</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7640.56</v>
+        <v>7613.16</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>8732.07</v>
+        <v>8713.17</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>24013.19</v>
+        <v>23961.23</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6549.05</v>
+        <v>6534.88</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2292.17</v>
+        <v>2287.21</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2396.49</v>
+        <v>2391.3</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>75314.11</v>
+        <v>75151.12</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>4366.04</v>
+        <v>4356.59</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>4366.04</v>
+        <v>4356.59</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5948.72</v>
+        <v>5935.85</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2292.17</v>
+        <v>2287.21</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>4366.04</v>
+        <v>4356.59</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>5457.54</v>
+        <v>5445.73</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>21830.18</v>
+        <v>21782.93</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3820.28</v>
+        <v>3812.01</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>13098.11</v>
+        <v>13069.76</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>10915.09</v>
+        <v>10891.47</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>10653.13</v>
+        <v>10630.07</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>7640.56</v>
+        <v>7624.03</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7640.56</v>
+        <v>7624.03</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2837.92</v>
+        <v>2831.78</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2292.17</v>
+        <v>2287.21</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4366.04</v>
+        <v>4356.59</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3274.53</v>
+        <v>3267.44</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2401.32</v>
+        <v>2396.12</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8732.07</v>
+        <v>8713.17</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>29289.55</v>
+        <v>29226.16</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>16372.63</v>
+        <v>16337.2</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2757</v>
+        <v>2751.03</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2292.17</v>
+        <v>2287.21</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2292.17</v>
+        <v>2287.21</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2728.77</v>
+        <v>2722.87</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2455.89</v>
+        <v>2450.58</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>11460.84</v>
+        <v>11436.04</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>5457.54</v>
+        <v>5445.73</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>5457.54</v>
+        <v>5434.66</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>32745.26</v>
+        <v>32607.99</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2401.32</v>
+        <v>2391.25</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3056.22</v>
+        <v>3043.41</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>11460.84</v>
+        <v>11412.8</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2292.17</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2277.43</v>
+        <v>2267.89</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2292.17</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>7640.56</v>
+        <v>7608.53</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>4473.71</v>
+        <v>4454.95</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2292.17</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>14189.61</v>
+        <v>14130.13</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2401.32</v>
+        <v>2391.25</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2292.17</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>5457.54</v>
+        <v>5434.66</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4366.04</v>
+        <v>4347.73</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>6549.05</v>
+        <v>6521.6</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2279.07</v>
+        <v>2269.52</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2281.25</v>
+        <v>2271.69</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3274.53</v>
+        <v>3260.8</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2728.77</v>
+        <v>2717.33</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>12875.96</v>
+        <v>12821.98</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3711.13</v>
+        <v>3695.57</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>5457.54</v>
+        <v>5434.66</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>37111.3</v>
+        <v>36955.72</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>7640.56</v>
+        <v>7608.53</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3274.53</v>
+        <v>3260.8</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>7422.26</v>
+        <v>7391.14</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>10915.09</v>
+        <v>10869.33</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3056.22</v>
+        <v>3043.41</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>4579.75</v>
+        <v>4560.56</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>43660.35</v>
+        <v>43477.32</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>54575.44</v>
+        <v>54346.64</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>14189.61</v>
+        <v>14025.4</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2292.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7640.56</v>
+        <v>7552.14</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3274.53</v>
+        <v>3236.63</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>5457.54</v>
+        <v>5394.38</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>10041.88</v>
+        <v>9925.67</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2292.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>54575.44</v>
+        <v>53943.83</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5457.54</v>
+        <v>5394.38</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2292.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>4911.79</v>
+        <v>4854.95</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>5457.54</v>
+        <v>5394.38</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>16809.24</v>
+        <v>16614.7</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2728.77</v>
+        <v>2697.19</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2292.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>21830.18</v>
+        <v>21577.53</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3820.28</v>
+        <v>3776.07</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>5457.54</v>
+        <v>5394.38</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3274.53</v>
+        <v>3236.63</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>25499.34</v>
+        <v>25204.23</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>16372.63</v>
+        <v>16183.15</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2728.77</v>
+        <v>2697.19</v>
       </c>
     </row>
     <row r="253">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>13098.11</v>
+        <v>12946.52</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2728.77</v>
+        <v>2697.19</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>7532.79</v>
+        <v>7445.61</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2292.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2401.32</v>
+        <v>2373.53</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>54575.44</v>
+        <v>53943.83</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>50209.41</v>
+        <v>49628.33</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>6549.05</v>
+        <v>6473.26</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>4366.04</v>
+        <v>4315.51</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>5457.54</v>
+        <v>5394.38</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3274.53</v>
+        <v>3236.63</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>5708.59</v>
+        <v>5642.53</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2728.77</v>
+        <v>2697.19</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>10915.09</v>
+        <v>10788.77</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>10915.09</v>
+        <v>10788.77</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2401.32</v>
+        <v>2373.53</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>3274.53</v>
+        <v>3236.63</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2277.17</v>
+        <v>2257.88</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>7980.31</v>
+        <v>7912.71</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>5457.54</v>
+        <v>5411.31</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>29219.44</v>
+        <v>28971.93</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>10915.09</v>
+        <v>10822.63</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3274.53</v>
+        <v>3246.79</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>10369.33</v>
+        <v>10281.5</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2277.17</v>
+        <v>2257.88</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>4191.43</v>
+        <v>4155.93</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>3274.53</v>
+        <v>3246.79</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>9823.58</v>
+        <v>9740.370000000001</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>3410.46</v>
+        <v>3381.57</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4224.14</v>
+        <v>4188.36</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>10915.09</v>
+        <v>10822.63</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2292.17</v>
+        <v>2272.75</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>10915.09</v>
+        <v>10822.63</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>2292.17</v>
+        <v>2272.75</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>2292.17</v>
+        <v>2272.75</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2292.17</v>
+        <v>2272.75</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2947.07</v>
+        <v>2922.11</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>4366.04</v>
+        <v>4329.05</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>4147.73</v>
+        <v>4112.6</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2837.92</v>
+        <v>2813.88</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3274.53</v>
+        <v>3246.79</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2277.17</v>
+        <v>2257.88</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3593.94</v>
+        <v>3563.49</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>6876.51</v>
+        <v>6818.26</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>4366.04</v>
+        <v>4329.05</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2923.07</v>
+        <v>2898.31</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>109150.88</v>
+        <v>108226.28</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2277.17</v>
+        <v>2257.88</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3274.53</v>
+        <v>3246.79</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>8732.07</v>
+        <v>8725.049999999999</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>6330.75</v>
+        <v>6325.66</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2292.17</v>
+        <v>2290.33</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>2292.17</v>
+        <v>2290.33</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>174641.41</v>
+        <v>174501.04</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>7640.56</v>
+        <v>7634.42</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>7483.38</v>
+        <v>7477.37</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>10915.09</v>
+        <v>10906.31</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>3274.53</v>
+        <v>3271.89</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3274.53</v>
+        <v>3271.89</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2292.17</v>
+        <v>2290.33</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>6147.96</v>
+        <v>6143.01</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>16372.63</v>
+        <v>16359.47</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>6549.05</v>
+        <v>6543.79</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>32745.26</v>
+        <v>32718.94</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2292.17</v>
+        <v>2290.33</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>3367.32</v>
+        <v>3364.61</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>5239.24</v>
+        <v>5235.03</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2728.77</v>
+        <v>2726.58</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2277.87</v>
+        <v>2276.04</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3274.53</v>
+        <v>3271.89</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2401.32</v>
+        <v>2399.39</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>7640.56</v>
+        <v>7634.42</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2281.25</v>
+        <v>2279.42</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>17464.14</v>
+        <v>17450.1</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>6267.03</v>
+        <v>6261.99</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>37111.3</v>
+        <v>37081.47</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>7640.56</v>
+        <v>7634.42</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>75859.86</v>
+        <v>75798.89</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>8732.07</v>
+        <v>8725.049999999999</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>4396.15</v>
+        <v>4413.02</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>4445.21</v>
+        <v>4462.27</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3820.28</v>
+        <v>3834.94</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2281.25</v>
+        <v>2290.01</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>10915.09</v>
+        <v>10956.98</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>5457.54</v>
+        <v>5478.49</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>6549.05</v>
+        <v>6574.19</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>8732.07</v>
+        <v>8765.59</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>5399.39</v>
+        <v>5420.11</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>27287.72</v>
+        <v>27392.46</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2292.17</v>
+        <v>2300.97</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>63307.51</v>
+        <v>63550.5</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>10915.09</v>
+        <v>10956.98</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>5457.54</v>
+        <v>5478.49</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>25104.7</v>
+        <v>25201.06</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2401.32</v>
+        <v>2410.54</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>8732.07</v>
+        <v>8765.59</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>5457.54</v>
+        <v>5478.49</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>7640.56</v>
+        <v>7669.89</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>3827.28</v>
+        <v>3841.97</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>6549.05</v>
+        <v>6574.19</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>16373.4</v>
+        <v>16436.24</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2277.17</v>
+        <v>2285.91</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>14189.61</v>
+        <v>14244.08</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>6549.05</v>
+        <v>6574.19</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>30234.79</v>
+        <v>30350.84</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2837.92</v>
+        <v>2848.82</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2292.17</v>
+        <v>2300.97</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>3110.8</v>
+        <v>3122.74</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>3274.53</v>
+        <v>3287.09</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2292.17</v>
+        <v>2300.97</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2866.85</v>
+        <v>2877.85</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>13098.11</v>
+        <v>13148.38</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>5409.7</v>
+        <v>5430.46</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>5457.54</v>
+        <v>5478.49</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>5506.66</v>
+        <v>5527.8</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2728.77</v>
+        <v>2739.25</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>3274.53</v>
+        <v>3287.09</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>27287.72</v>
+        <v>27392.46</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>32745.26</v>
+        <v>32870.95</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>15499.43</v>
+        <v>15558.92</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2401.32</v>
+        <v>2410.54</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2292.17</v>
+        <v>2300.97</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>2401.32</v>
+        <v>2412.2</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2281.25</v>
+        <v>2291.59</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>6549.05</v>
+        <v>6578.73</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>5457.54</v>
+        <v>5482.28</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2597.79</v>
+        <v>2609.56</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4638.91</v>
+        <v>4659.93</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>32745.26</v>
+        <v>32893.65</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>2292.17</v>
+        <v>2302.56</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>43660.35</v>
+        <v>43858.21</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2597.79</v>
+        <v>2609.56</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>21830.18</v>
+        <v>21929.1</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>6549.05</v>
+        <v>6578.73</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>16372.63</v>
+        <v>16446.83</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3036.07</v>
+        <v>3049.83</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2292.17</v>
+        <v>2302.56</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>7640.56</v>
+        <v>7675.19</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>3846.46</v>
+        <v>3863.89</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>32745.26</v>
+        <v>32893.65</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>16372.63</v>
+        <v>16446.83</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2292.17</v>
+        <v>2302.56</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>7179.02</v>
+        <v>7211.55</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>5457.54</v>
+        <v>5482.28</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>6549.05</v>
+        <v>6578.73</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>2837.92</v>
+        <v>2850.78</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>27287.72</v>
+        <v>27411.38</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>21469.12</v>
+        <v>21566.41</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>5130.09</v>
+        <v>5153.34</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>6003.3</v>
+        <v>6030.5</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>5457.54</v>
+        <v>5482.28</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>10915.09</v>
+        <v>10964.55</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>16372.63</v>
+        <v>16446.83</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>75146.64999999999</v>
+        <v>75487.19</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>36608.57</v>
+        <v>36774.47</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>6615.18</v>
+        <v>6645.15</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2292.17</v>
+        <v>2302.56</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>10478.48</v>
+        <v>10525.97</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>4366.04</v>
+        <v>4385.82</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>14407.92</v>
+        <v>14473.21</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2401.32</v>
+        <v>2412.2</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>5566.7</v>
+        <v>5591.92</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2728.77</v>
+        <v>2741.14</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>2401.32</v>
+        <v>2412.2</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>4366.04</v>
+        <v>4385.82</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>13098.11</v>
+        <v>13157.46</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>6658.2</v>
+        <v>6688.38</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>24013.19</v>
+        <v>24122.01</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>3492.83</v>
+        <v>3508.66</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>11460.84</v>
+        <v>11512.78</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>2281.25</v>
+        <v>2287.3</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2336.19</v>
+        <v>2342.39</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2728.77</v>
+        <v>2736.01</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>3274.53</v>
+        <v>3283.21</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>62936.4</v>
+        <v>63103.29</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>4256.88</v>
+        <v>4268.17</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>24668.1</v>
+        <v>24733.51</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>16372.63</v>
+        <v>16416.05</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2728.77</v>
+        <v>2736.01</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>3274.53</v>
+        <v>3283.21</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>6003.3</v>
+        <v>6019.22</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>2427.13</v>
+        <v>2433.57</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>52392.42</v>
+        <v>52531.35</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2277.98</v>
+        <v>2284.02</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>3274.53</v>
+        <v>3283.21</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>5457.54</v>
+        <v>5472.02</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>4366.04</v>
+        <v>4377.61</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>17464.14</v>
+        <v>17510.45</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2971.26</v>
+        <v>2979.14</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>75859.86</v>
+        <v>76061.02</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>2510.47</v>
+        <v>2517.13</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2292.17</v>
+        <v>2298.25</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>22921.69</v>
+        <v>22982.47</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>4911.79</v>
+        <v>4924.81</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>4242.69</v>
+        <v>4253.95</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>2281.25</v>
+        <v>2287.3</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>2292.17</v>
+        <v>2298.25</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>74222.60000000001</v>
+        <v>74419.42</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>3274.53</v>
+        <v>3283.21</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2292.17</v>
+        <v>2298.25</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2292.17</v>
+        <v>2298.25</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>5457.54</v>
+        <v>5472.02</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>4366.04</v>
+        <v>4377.61</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>6549.05</v>
+        <v>6566.42</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>2277.17</v>
+        <v>2283.21</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>4582.66</v>
+        <v>4594.81</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>10915.09</v>
+        <v>10944.03</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>2277.17</v>
+        <v>2283.21</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>13078.46</v>
+        <v>13113.14</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>16372.63</v>
+        <v>16416.05</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3929.43</v>
+        <v>3923.92</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>4366.04</v>
+        <v>4359.91</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>5457.54</v>
+        <v>5449.89</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>16263.48</v>
+        <v>16240.67</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>4366.04</v>
+        <v>4359.91</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>48102.79</v>
+        <v>48035.32</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>65490.53</v>
+        <v>65398.66</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>8732.07</v>
+        <v>8719.82</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>9823.309999999999</v>
+        <v>9809.530000000001</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>4366.04</v>
+        <v>4359.91</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>25428.11</v>
+        <v>25392.44</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>4675.23</v>
+        <v>4668.67</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>16639.09</v>
+        <v>16615.75</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>5457.54</v>
+        <v>5449.89</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>43660.35</v>
+        <v>43599.11</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>2280.57</v>
+        <v>2277.37</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>10915.09</v>
+        <v>10899.78</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>21830.18</v>
+        <v>21799.55</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>21830.18</v>
+        <v>21799.55</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2947.07</v>
+        <v>2942.94</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>11460.84</v>
+        <v>11444.77</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>25104.7</v>
+        <v>25069.49</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>4366.04</v>
+        <v>4359.91</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>2347.91</v>
+        <v>2344.62</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>10915.09</v>
+        <v>10899.78</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>4366.04</v>
+        <v>4359.91</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>10369.33</v>
+        <v>10354.79</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>4582.69</v>
+        <v>4576.26</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>9774.73</v>
+        <v>9761.02</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>2841.07</v>
+        <v>2837.09</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>3820.28</v>
+        <v>3814.92</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>7640.56</v>
+        <v>7629.84</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>3914.22</v>
+        <v>3908.73</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>2551.55</v>
+        <v>2547.97</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2277.17</v>
+        <v>2273.98</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2292.17</v>
+        <v>2295.11</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2292.17</v>
+        <v>2295.11</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>3820.28</v>
+        <v>3825.18</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>4594.49</v>
+        <v>4600.38</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>36019.79</v>
+        <v>36065.97</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>11118.6</v>
+        <v>11132.86</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>9823.58</v>
+        <v>9836.17</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>6549.05</v>
+        <v>6557.45</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>3820.28</v>
+        <v>3825.18</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>38202.73</v>
+        <v>38251.71</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>2279.7</v>
+        <v>2282.62</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>17464.14</v>
+        <v>17486.53</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>4556.67</v>
+        <v>4562.51</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2292.17</v>
+        <v>2295.11</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>7640.56</v>
+        <v>7650.36</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>6549.05</v>
+        <v>6557.45</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>2292.17</v>
+        <v>2295.11</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>10915.09</v>
+        <v>10929.08</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>43660.35</v>
+        <v>43716.32</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>2281.25</v>
+        <v>2284.18</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>20738.67</v>
+        <v>20765.25</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>3274.53</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>5216.75</v>
+        <v>5223.44</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>8732.07</v>
+        <v>8743.26</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>4911.79</v>
+        <v>4918.09</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>10915.09</v>
+        <v>10929.08</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>3274.53</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>3274.53</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>3681.29</v>
+        <v>3686.01</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>3274.53</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>18555.65</v>
+        <v>18579.44</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>3274.53</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>10915.09</v>
+        <v>10929.08</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>22577.65</v>
+        <v>22606.59</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>4366.04</v>
+        <v>4371.63</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>12006.6</v>
+        <v>12021.99</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>2292.17</v>
+        <v>2295.11</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>2292.17</v>
+        <v>2307.95</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>33760.37</v>
+        <v>33992.75</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>3274.53</v>
+        <v>3297.07</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>3820.28</v>
+        <v>3846.58</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>48026.39</v>
+        <v>48356.96</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>21830.18</v>
+        <v>21980.44</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>37657.05</v>
+        <v>37916.25</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>4366.04</v>
+        <v>4396.09</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>27287.72</v>
+        <v>27475.55</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>13016.54</v>
+        <v>13106.13</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>2728.77</v>
+        <v>2747.55</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>5457.54</v>
+        <v>5495.11</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>9585.84</v>
+        <v>9651.83</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>11114.72</v>
+        <v>11191.22</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>21830.18</v>
+        <v>21980.44</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>18555.65</v>
+        <v>18683.37</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>2292.17</v>
+        <v>2307.95</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>2760.7</v>
+        <v>2779.7</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>4147.73</v>
+        <v>4176.28</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>5457.54</v>
+        <v>5495.11</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>3072.06</v>
+        <v>3093.2</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>70948.07000000001</v>
+        <v>71436.42</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>8857.58</v>
+        <v>8918.549999999999</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>4366.04</v>
+        <v>4396.09</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>27287.72</v>
+        <v>27475.55</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>3274.53</v>
+        <v>3297.07</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>24013.19</v>
+        <v>24178.48</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2292.17</v>
+        <v>2307.95</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>3518.2</v>
+        <v>3542.42</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2292.17</v>
+        <v>2307.95</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>17464.14</v>
+        <v>17584.35</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2292.17</v>
+        <v>2307.95</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>2277.17</v>
+        <v>2292.85</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>5457.54</v>
+        <v>5495.11</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>2277.17</v>
+        <v>2292.85</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>74222.60000000001</v>
+        <v>74733.49000000001</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>75146.64999999999</v>
+        <v>75663.89999999999</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2292.17</v>
+        <v>2307.95</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>4911.79</v>
+        <v>4945.6</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>3078.05</v>
+        <v>3099.24</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>7640.56</v>
+        <v>7693.15</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>6549.05</v>
+        <v>6594.13</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>13098.11</v>
+        <v>13188.26</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>32745.26</v>
+        <v>32970.66</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>2376.9</v>
+        <v>2393.26</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>13971.31</v>
+        <v>14067.48</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>4038.58</v>
+        <v>4066.38</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>4827.35</v>
+        <v>4860.57</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>13906.91</v>
+        <v>14002.64</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>2277.17</v>
+        <v>2296.63</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>11810.13</v>
+        <v>11911.05</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>3274.53</v>
+        <v>3302.51</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>11834.14</v>
+        <v>11935.27</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>3938.71</v>
+        <v>3972.37</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>3820.28</v>
+        <v>3852.93</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>3274.53</v>
+        <v>3302.51</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>6549.05</v>
+        <v>6605.02</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>5457.54</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>3492.83</v>
+        <v>3522.68</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>5457.54</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>2534.85</v>
+        <v>2556.51</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>43660.35</v>
+        <v>44033.47</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>5457.54</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>13098.11</v>
+        <v>13210.04</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>2401.32</v>
+        <v>2421.84</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>12443.2</v>
+        <v>12549.54</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>3274.53</v>
+        <v>3302.51</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>18555.65</v>
+        <v>18714.22</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>10915.09</v>
+        <v>11008.37</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>65490.53</v>
+        <v>66050.2</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>13098.11</v>
+        <v>13210.04</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>6549.05</v>
+        <v>6605.02</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>2281.25</v>
+        <v>2300.75</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2563.04</v>
+        <v>2584.94</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>2281.25</v>
+        <v>2300.75</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>2401.32</v>
+        <v>2421.84</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>3358.49</v>
+        <v>3387.19</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>5457.54</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>3795.45</v>
+        <v>3827.89</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>2277.98</v>
+        <v>2297.45</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2619.62</v>
+        <v>2642.01</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>4911.79</v>
+        <v>4953.76</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>37111.3</v>
+        <v>37428.45</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>5476.21</v>
+        <v>5523</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>2510.47</v>
+        <v>2531.92</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>3165.38</v>
+        <v>3192.43</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>2624.21</v>
+        <v>2646.64</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>19647.16</v>
+        <v>19815.06</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>19535.28</v>
+        <v>19702.22</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>4911.79</v>
+        <v>4953.76</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>7142.78</v>
+        <v>7203.82</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>3366.21</v>
+        <v>3394.98</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>16372.63</v>
+        <v>16512.55</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>6549.05</v>
+        <v>6605.02</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>24186.74</v>
+        <v>24393.44</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>8732.07</v>
+        <v>8806.690000000001</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>22921.69</v>
+        <v>23117.57</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>8841.219999999999</v>
+        <v>8916.780000000001</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>4240.51</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>6682.06</v>
+        <v>6753.74</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>62216</v>
+        <v>62883.37</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>21830.18</v>
+        <v>22064.34</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>10915.09</v>
+        <v>11032.17</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>10915.09</v>
+        <v>11032.17</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>2277.34</v>
+        <v>2301.77</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>3274.53</v>
+        <v>3309.65</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>3274.53</v>
+        <v>3309.65</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>3274.53</v>
+        <v>3309.65</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>3274.53</v>
+        <v>3309.65</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>2401.32</v>
+        <v>2427.08</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>6921.94</v>
+        <v>6996.19</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2933.35</v>
+        <v>2964.81</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>10915.09</v>
+        <v>11032.17</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>3916.48</v>
+        <v>3958.49</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>6555.27</v>
+        <v>6625.58</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>5457.54</v>
+        <v>5516.08</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>27287.72</v>
+        <v>27580.42</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>10969.66</v>
+        <v>11087.33</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>6549.05</v>
+        <v>6619.3</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>6549.05</v>
+        <v>6619.3</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>30025.72</v>
+        <v>30347.79</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>17027.54</v>
+        <v>17210.18</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>3618.77</v>
+        <v>3657.58</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>4366.04</v>
+        <v>4412.87</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>4366.04</v>
+        <v>4412.87</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>27768.95</v>
+        <v>28066.82</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>3056.22</v>
+        <v>3089.01</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>4366.04</v>
+        <v>4419.69</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>5790.05</v>
+        <v>5861.21</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>2281.25</v>
+        <v>2309.29</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>2401.32</v>
+        <v>2430.83</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>24271.47</v>
+        <v>24569.76</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>23178.65</v>
+        <v>23463.51</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>4426.34</v>
+        <v>4480.74</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>3649.72</v>
+        <v>3694.58</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>10368.48</v>
+        <v>10495.91</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>3772.05</v>
+        <v>3818.41</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>6727.88</v>
+        <v>6810.57</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>2697.88</v>
+        <v>2731.04</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>4366.04</v>
+        <v>4419.69</v>
       </c>
     </row>
     <row r="704">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2292.17</v>
+        <v>2320.34</v>
       </c>
     </row>
     <row r="705">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2510.47</v>
+        <v>2541.32</v>
       </c>
     </row>
     <row r="706">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2292.17</v>
+        <v>2320.34</v>
       </c>
     </row>
     <row r="707">
@@ -43578,7 +43578,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>28207.61</v>
+        <v>28554.28</v>
       </c>
     </row>
     <row r="708">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>13643.86</v>
+        <v>13811.54</v>
       </c>
     </row>
     <row r="709">
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>2292.17</v>
+        <v>2320.34</v>
       </c>
     </row>
     <row r="710">
@@ -43761,7 +43761,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>2827.01</v>
+        <v>2861.75</v>
       </c>
     </row>
     <row r="711">
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>34665.96</v>
+        <v>35092.01</v>
       </c>
     </row>
     <row r="712">
@@ -43883,7 +43883,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>2292.17</v>
+        <v>2320.34</v>
       </c>
     </row>
     <row r="713">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>35474.04</v>
+        <v>35910.02</v>
       </c>
     </row>
     <row r="714">
@@ -44005,7 +44005,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>2949.31</v>
+        <v>2985.56</v>
       </c>
     </row>
     <row r="715">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>9168.67</v>
+        <v>9281.360000000001</v>
       </c>
     </row>
     <row r="716">
@@ -44127,7 +44127,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>5457.54</v>
+        <v>5524.62</v>
       </c>
     </row>
     <row r="717">
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>2401.32</v>
+        <v>2430.83</v>
       </c>
     </row>
     <row r="718">
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>10915.09</v>
+        <v>11049.24</v>
       </c>
     </row>
     <row r="719">
@@ -44310,7 +44310,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>21830.18</v>
+        <v>22098.47</v>
       </c>
     </row>
     <row r="720">
@@ -44371,7 +44371,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>17464.14</v>
+        <v>17678.78</v>
       </c>
     </row>
     <row r="721">
@@ -44432,7 +44432,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>4911.79</v>
+        <v>4972.16</v>
       </c>
     </row>
     <row r="722">
@@ -44493,7 +44493,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>4366.04</v>
+        <v>4419.69</v>
       </c>
     </row>
     <row r="723">
@@ -44554,7 +44554,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>74222.60000000001</v>
+        <v>75134.8</v>
       </c>
     </row>
     <row r="724">
@@ -44615,7 +44615,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>5142.02</v>
+        <v>5205.22</v>
       </c>
     </row>
     <row r="725">
@@ -44676,7 +44676,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>18555.65</v>
+        <v>18783.7</v>
       </c>
     </row>
     <row r="726">
@@ -44737,7 +44737,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>2728.77</v>
+        <v>2762.31</v>
       </c>
     </row>
     <row r="727">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>4366.04</v>
+        <v>4419.69</v>
       </c>
     </row>
     <row r="728">
@@ -44859,7 +44859,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>2292.17</v>
+        <v>2320.34</v>
       </c>
     </row>
     <row r="729">
@@ -44920,7 +44920,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2292.17</v>
+        <v>2320.34</v>
       </c>
     </row>
     <row r="730">
@@ -44981,7 +44981,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>2278.26</v>
+        <v>2306.26</v>
       </c>
     </row>
     <row r="731">
@@ -45042,7 +45042,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>10915.09</v>
+        <v>11049.24</v>
       </c>
     </row>
     <row r="732">
@@ -45103,7 +45103,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>6549.05</v>
+        <v>6629.54</v>
       </c>
     </row>
     <row r="733">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>11241.03</v>
+        <v>11379.19</v>
       </c>
     </row>
     <row r="734">
@@ -45225,7 +45225,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>21830.18</v>
+        <v>22098.47</v>
       </c>
     </row>
     <row r="735">
@@ -45286,7 +45286,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>3892.29</v>
+        <v>3940.13</v>
       </c>
     </row>
     <row r="736">
@@ -45347,7 +45347,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>6112.45</v>
+        <v>6187.57</v>
       </c>
     </row>
     <row r="737">
@@ -45408,7 +45408,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>16584.31</v>
+        <v>16788.13</v>
       </c>
     </row>
     <row r="738">
@@ -45469,7 +45469,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>9496.129999999999</v>
+        <v>9612.83</v>
       </c>
     </row>
     <row r="739">
@@ -45530,7 +45530,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>11002.71</v>
+        <v>11137.93</v>
       </c>
     </row>
     <row r="740">
@@ -45591,7 +45591,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>12817.04</v>
+        <v>12974.56</v>
       </c>
     </row>
     <row r="741">
@@ -45652,7 +45652,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>7640.56</v>
+        <v>7734.46</v>
       </c>
     </row>
     <row r="742">
@@ -45713,7 +45713,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>3360.02</v>
+        <v>3401.31</v>
       </c>
     </row>
     <row r="743">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>2906.28</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="744">
@@ -45835,7 +45835,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="745">
@@ -45896,7 +45896,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>2728.77</v>
+        <v>2763.84</v>
       </c>
     </row>
     <row r="746">
@@ -45957,7 +45957,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>7094.81</v>
+        <v>7185.97</v>
       </c>
     </row>
     <row r="747">
@@ -46018,7 +46018,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>10478.48</v>
+        <v>10613.13</v>
       </c>
     </row>
     <row r="748">
@@ -46079,7 +46079,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>14189.61</v>
+        <v>14371.95</v>
       </c>
     </row>
     <row r="749">
@@ -46140,7 +46140,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="750">
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="751">
@@ -46262,7 +46262,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>2281.25</v>
+        <v>2310.57</v>
       </c>
     </row>
     <row r="752">
@@ -46323,7 +46323,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>2509.43</v>
+        <v>2541.68</v>
       </c>
     </row>
     <row r="753">
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="754">
@@ -46445,7 +46445,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>21830.18</v>
+        <v>22110.69</v>
       </c>
     </row>
     <row r="755">
@@ -46506,7 +46506,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>11351.69</v>
+        <v>11497.56</v>
       </c>
     </row>
     <row r="756">
@@ -46567,7 +46567,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>2510.47</v>
+        <v>2542.73</v>
       </c>
     </row>
     <row r="757">
@@ -46628,7 +46628,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="758">
@@ -46689,7 +46689,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>27287.72</v>
+        <v>27638.36</v>
       </c>
     </row>
     <row r="759">
@@ -46750,7 +46750,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>7640.56</v>
+        <v>7738.74</v>
       </c>
     </row>
     <row r="760">
@@ -46811,7 +46811,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>45843.37</v>
+        <v>46432.44</v>
       </c>
     </row>
     <row r="761">
@@ -46872,7 +46872,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>10915.09</v>
+        <v>11055.34</v>
       </c>
     </row>
     <row r="762">
@@ -46933,7 +46933,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>4457.11</v>
+        <v>4514.38</v>
       </c>
     </row>
     <row r="763">
@@ -46994,7 +46994,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>5873.21</v>
+        <v>5948.68</v>
       </c>
     </row>
     <row r="764">
@@ -47055,7 +47055,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>20738.67</v>
+        <v>21005.15</v>
       </c>
     </row>
     <row r="765">
@@ -47116,7 +47116,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>16372.63</v>
+        <v>16583.01</v>
       </c>
     </row>
     <row r="766">
@@ -47177,7 +47177,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>8732.07</v>
+        <v>8844.27</v>
       </c>
     </row>
     <row r="767">
@@ -47238,7 +47238,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>10915.09</v>
+        <v>11055.34</v>
       </c>
     </row>
     <row r="768">
@@ -47299,7 +47299,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>21830.18</v>
+        <v>22110.69</v>
       </c>
     </row>
     <row r="769">
@@ -47360,7 +47360,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>10915.09</v>
+        <v>11055.34</v>
       </c>
     </row>
     <row r="770">
@@ -47421,7 +47421,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>2837.92</v>
+        <v>2874.39</v>
       </c>
     </row>
     <row r="771">
@@ -47482,7 +47482,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>4618.79</v>
+        <v>4678.14</v>
       </c>
     </row>
     <row r="772">
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>9823.58</v>
+        <v>9949.809999999999</v>
       </c>
     </row>
     <row r="773">
@@ -47604,7 +47604,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>4693.49</v>
+        <v>4753.8</v>
       </c>
     </row>
     <row r="774">
@@ -47665,7 +47665,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>2360.29</v>
+        <v>2390.62</v>
       </c>
     </row>
     <row r="775">
@@ -47726,7 +47726,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>3820.28</v>
+        <v>3869.37</v>
       </c>
     </row>
     <row r="776">
@@ -47787,7 +47787,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>8732.07</v>
+        <v>8844.27</v>
       </c>
     </row>
     <row r="777">
@@ -47848,7 +47848,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>8732.07</v>
+        <v>8844.27</v>
       </c>
     </row>
     <row r="778">
@@ -47909,7 +47909,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="779">
@@ -47970,7 +47970,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>16372.63</v>
+        <v>16583.01</v>
       </c>
     </row>
     <row r="780">
@@ -48031,7 +48031,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>13098.11</v>
+        <v>13266.41</v>
       </c>
     </row>
     <row r="781">
@@ -48092,7 +48092,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>5457.54</v>
+        <v>5527.67</v>
       </c>
     </row>
     <row r="782">
@@ -48153,7 +48153,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="783">
@@ -48214,7 +48214,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>13401.98</v>
+        <v>13574.19</v>
       </c>
     </row>
     <row r="784">
@@ -48275,7 +48275,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>2728.77</v>
+        <v>2763.84</v>
       </c>
     </row>
     <row r="785">
@@ -48336,7 +48336,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>27287.72</v>
+        <v>27638.36</v>
       </c>
     </row>
     <row r="786">
@@ -48397,7 +48397,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>16372.63</v>
+        <v>16583.01</v>
       </c>
     </row>
     <row r="787">
@@ -48458,7 +48458,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>5457.54</v>
+        <v>5527.67</v>
       </c>
     </row>
     <row r="788">
@@ -48519,7 +48519,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>2728.77</v>
+        <v>2763.84</v>
       </c>
     </row>
     <row r="789">
@@ -48580,7 +48580,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>9714.43</v>
+        <v>9839.26</v>
       </c>
     </row>
     <row r="790">
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="791">
@@ -48702,7 +48702,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>21830.18</v>
+        <v>22110.69</v>
       </c>
     </row>
     <row r="792">
@@ -48763,7 +48763,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>22594.23</v>
+        <v>22884.56</v>
       </c>
     </row>
     <row r="793">
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="794">
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="795">
@@ -48946,7 +48946,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="796">
@@ -49007,7 +49007,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="797">
@@ -49068,7 +49068,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>3206.45</v>
+        <v>3223.99</v>
       </c>
     </row>
     <row r="798">
@@ -49129,7 +49129,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>3599.14</v>
+        <v>3618.82</v>
       </c>
     </row>
     <row r="799">
@@ -49190,7 +49190,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>62216</v>
+        <v>62556.25</v>
       </c>
     </row>
     <row r="800">
@@ -49251,7 +49251,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>4256.88</v>
+        <v>4280.16</v>
       </c>
     </row>
     <row r="801">
@@ -49312,7 +49312,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>5666.24</v>
+        <v>5697.23</v>
       </c>
     </row>
     <row r="802">
@@ -49373,7 +49373,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>2292.17</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="803">
@@ -49434,7 +49434,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="804">
@@ -49495,7 +49495,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="805">
@@ -49556,7 +49556,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>4569.98</v>
+        <v>4594.98</v>
       </c>
     </row>
     <row r="806">
@@ -49617,7 +49617,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>65490.53</v>
+        <v>65848.67999999999</v>
       </c>
     </row>
     <row r="807">
@@ -49678,7 +49678,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>4888.35</v>
+        <v>4915.09</v>
       </c>
     </row>
     <row r="808">
@@ -49739,7 +49739,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>3777.66</v>
+        <v>3798.32</v>
       </c>
     </row>
     <row r="809">
@@ -49800,7 +49800,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>54575.44</v>
+        <v>54873.9</v>
       </c>
     </row>
     <row r="810">
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>5457.54</v>
+        <v>5487.39</v>
       </c>
     </row>
     <row r="811">
@@ -49922,7 +49922,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>2728.77</v>
+        <v>2743.69</v>
       </c>
     </row>
     <row r="812">
@@ -49983,7 +49983,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>10634.1</v>
+        <v>10692.26</v>
       </c>
     </row>
     <row r="813">
@@ -50044,7 +50044,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>3383.68</v>
+        <v>3402.18</v>
       </c>
     </row>
     <row r="814">
@@ -50105,7 +50105,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>17572.2</v>
+        <v>17668.3</v>
       </c>
     </row>
     <row r="815">
@@ -50166,7 +50166,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>6549.05</v>
+        <v>6584.87</v>
       </c>
     </row>
     <row r="816">
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>3339.73</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="817">
@@ -50288,7 +50288,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>5457.54</v>
+        <v>5487.39</v>
       </c>
     </row>
     <row r="818">
@@ -50349,7 +50349,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>2292.17</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="819">
@@ -50410,7 +50410,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>3056.95</v>
+        <v>3073.67</v>
       </c>
     </row>
     <row r="820">
@@ -50471,7 +50471,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>8732.07</v>
+        <v>8779.82</v>
       </c>
     </row>
     <row r="821">
@@ -50532,7 +50532,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>3820.28</v>
+        <v>3841.17</v>
       </c>
     </row>
     <row r="822">
@@ -50593,7 +50593,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>5824.14</v>
+        <v>5855.99</v>
       </c>
     </row>
     <row r="823">
@@ -50654,7 +50654,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>3535.19</v>
+        <v>3554.53</v>
       </c>
     </row>
     <row r="824">
@@ -50715,7 +50715,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>2437.65</v>
+        <v>2450.98</v>
       </c>
     </row>
     <row r="825">
@@ -50776,7 +50776,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>2292.17</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="826">
@@ -50837,7 +50837,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>7101.92</v>
+        <v>7140.76</v>
       </c>
     </row>
     <row r="827">
@@ -50898,7 +50898,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="828">
@@ -50959,7 +50959,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>5595.75</v>
+        <v>5626.35</v>
       </c>
     </row>
     <row r="829">
@@ -51020,7 +51020,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>3927.21</v>
+        <v>3948.68</v>
       </c>
     </row>
     <row r="830">
@@ -51081,7 +51081,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="831">
@@ -51142,7 +51142,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>9516.33</v>
+        <v>9568.370000000001</v>
       </c>
     </row>
     <row r="832">
@@ -51203,7 +51203,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>2363.2</v>
+        <v>2376.13</v>
       </c>
     </row>
     <row r="833">
@@ -51264,7 +51264,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>4038.58</v>
+        <v>4060.67</v>
       </c>
     </row>
     <row r="834">
@@ -51325,7 +51325,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="835">
@@ -51386,7 +51386,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>43660.35</v>
+        <v>43899.12</v>
       </c>
     </row>
     <row r="836">
@@ -51447,7 +51447,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>4069.41</v>
+        <v>4091.67</v>
       </c>
     </row>
     <row r="837">
@@ -51508,7 +51508,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>13309.93</v>
+        <v>13382.72</v>
       </c>
     </row>
     <row r="838">
@@ -51569,7 +51569,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>2277.98</v>
+        <v>2290.44</v>
       </c>
     </row>
     <row r="839">
@@ -51630,7 +51630,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>2398.42</v>
+        <v>2411.54</v>
       </c>
     </row>
     <row r="840">
@@ -51691,7 +51691,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="841">
@@ -51752,7 +51752,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>37539.17</v>
+        <v>37744.46</v>
       </c>
     </row>
     <row r="842">
@@ -51813,7 +51813,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>6549.05</v>
+        <v>6584.87</v>
       </c>
     </row>
     <row r="843">
@@ -51874,7 +51874,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>6734.23</v>
+        <v>6771.06</v>
       </c>
     </row>
     <row r="844">
@@ -51935,7 +51935,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="845">
@@ -51996,7 +51996,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>13098.11</v>
+        <v>13169.74</v>
       </c>
     </row>
     <row r="846">
@@ -52057,7 +52057,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>6662.45</v>
+        <v>6698.88</v>
       </c>
     </row>
     <row r="847">
@@ -52118,7 +52118,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>54575.44</v>
+        <v>54873.9</v>
       </c>
     </row>
     <row r="848">
@@ -52179,7 +52179,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="849">
@@ -52240,7 +52240,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>5457.54</v>
+        <v>5487.39</v>
       </c>
     </row>
     <row r="850">
@@ -52301,7 +52301,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>33836.77</v>
+        <v>34021.82</v>
       </c>
     </row>
     <row r="851">
@@ -52362,7 +52362,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="852">
@@ -52423,7 +52423,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>6549.05</v>
+        <v>6584.87</v>
       </c>
     </row>
     <row r="853">
@@ -52484,7 +52484,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>2826.01</v>
+        <v>2841.46</v>
       </c>
     </row>
     <row r="854">
@@ -52545,7 +52545,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>21247.31</v>
+        <v>21363.51</v>
       </c>
     </row>
     <row r="855">
@@ -52606,7 +52606,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>4256.88</v>
+        <v>4280.16</v>
       </c>
     </row>
     <row r="856">
@@ -52667,7 +52667,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>4911.79</v>
+        <v>4938.65</v>
       </c>
     </row>
     <row r="857">
@@ -52728,7 +52728,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>8568.34</v>
+        <v>8615.200000000001</v>
       </c>
     </row>
     <row r="858">
@@ -52789,7 +52789,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>2292.17</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="859">
@@ -52850,7 +52850,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>75859.86</v>
+        <v>76274.72</v>
       </c>
     </row>
     <row r="860">
@@ -52911,7 +52911,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>8609.549999999999</v>
+        <v>8656.629999999999</v>
       </c>
     </row>
     <row r="861">
@@ -52972,7 +52972,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>2277.17</v>
+        <v>2289.62</v>
       </c>
     </row>
     <row r="862">
@@ -53033,7 +53033,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="863">
@@ -53094,7 +53094,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>7531.41</v>
+        <v>7572.6</v>
       </c>
     </row>
     <row r="864">
@@ -53155,7 +53155,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="865">
@@ -53216,7 +53216,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>2292.17</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="866">
@@ -53277,7 +53277,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>9594.940000000001</v>
+        <v>9647.41</v>
       </c>
     </row>
     <row r="867">
@@ -53338,7 +53338,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>2401.32</v>
+        <v>2414.45</v>
       </c>
     </row>
     <row r="868">
@@ -53399,7 +53399,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>7034.5</v>
+        <v>7072.97</v>
       </c>
     </row>
     <row r="869">
@@ -53460,7 +53460,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>4366.04</v>
+        <v>4389.91</v>
       </c>
     </row>
     <row r="870">
@@ -53521,7 +53521,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>41613.48</v>
+        <v>41841.06</v>
       </c>
     </row>
     <row r="871">
@@ -53582,7 +53582,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>5239.24</v>
+        <v>5267.89</v>
       </c>
     </row>
     <row r="872">
@@ -53643,7 +53643,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>8841.219999999999</v>
+        <v>8889.57</v>
       </c>
     </row>
     <row r="873">
@@ -53704,7 +53704,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>2654.61</v>
+        <v>2669.13</v>
       </c>
     </row>
     <row r="874">
@@ -53765,7 +53765,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>4366.04</v>
+        <v>4389.91</v>
       </c>
     </row>
     <row r="875">
@@ -53826,7 +53826,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>3103.88</v>
+        <v>3120.86</v>
       </c>
     </row>
     <row r="876">
@@ -53887,7 +53887,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>3141.02</v>
+        <v>3158.2</v>
       </c>
     </row>
     <row r="877">
@@ -53948,7 +53948,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>21830.18</v>
+        <v>21949.56</v>
       </c>
     </row>
     <row r="878">
@@ -54009,7 +54009,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>27287.72</v>
+        <v>27436.95</v>
       </c>
     </row>
     <row r="879">
@@ -54070,7 +54070,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>7351.29</v>
+        <v>7391.5</v>
       </c>
     </row>
     <row r="880">
@@ -54131,7 +54131,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>5457.54</v>
+        <v>5487.39</v>
       </c>
     </row>
     <row r="881">
@@ -54192,7 +54192,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>5457.54</v>
+        <v>5487.39</v>
       </c>
     </row>
     <row r="882">
@@ -54253,7 +54253,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>3489.12</v>
+        <v>3508.2</v>
       </c>
     </row>
     <row r="883">
@@ -54314,7 +54314,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>5015.43</v>
+        <v>5042.86</v>
       </c>
     </row>
     <row r="884">
@@ -54375,7 +54375,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>8732.07</v>
+        <v>8779.82</v>
       </c>
     </row>
     <row r="885">
@@ -54436,7 +54436,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="886">
@@ -54497,7 +54497,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>6549.05</v>
+        <v>6584.87</v>
       </c>
     </row>
     <row r="887">
@@ -54558,7 +54558,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>4366.04</v>
+        <v>4389.91</v>
       </c>
     </row>
     <row r="888">
@@ -54619,7 +54619,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="889">
@@ -54680,7 +54680,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>5398.31</v>
+        <v>5427.83</v>
       </c>
     </row>
     <row r="890">
@@ -54741,7 +54741,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="891">
@@ -54802,7 +54802,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="892">
@@ -54863,7 +54863,7 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="893">
@@ -54924,7 +54924,7 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="894">
@@ -54985,7 +54985,7 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>4892.79</v>
+        <v>4919.55</v>
       </c>
     </row>
     <row r="895">
@@ -55046,7 +55046,7 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>8186.32</v>
+        <v>8231.08</v>
       </c>
     </row>
     <row r="896">
@@ -55107,7 +55107,7 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>27270.5</v>
+        <v>27419.63</v>
       </c>
     </row>
     <row r="897">
@@ -55168,7 +55168,7 @@
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>54575.44</v>
+        <v>54873.9</v>
       </c>
     </row>
     <row r="898">
@@ -55229,7 +55229,7 @@
         </is>
       </c>
       <c r="M898" s="2" t="n">
-        <v>3493.45</v>
+        <v>3512.55</v>
       </c>
     </row>
     <row r="899">
@@ -55290,7 +55290,7 @@
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="900">
@@ -55351,7 +55351,7 @@
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>2859.75</v>
+        <v>2875.39</v>
       </c>
     </row>
     <row r="901">
@@ -55412,7 +55412,7 @@
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>15936.03</v>
+        <v>16023.18</v>
       </c>
     </row>
     <row r="902">
@@ -55473,7 +55473,7 @@
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="903">
@@ -55534,7 +55534,7 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>27287.72</v>
+        <v>27436.95</v>
       </c>
     </row>
     <row r="904">
@@ -55595,7 +55595,7 @@
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>3003.08</v>
+        <v>3019.5</v>
       </c>
     </row>
     <row r="905">
@@ -55656,7 +55656,7 @@
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="906">
@@ -55717,7 +55717,7 @@
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>10915.09</v>
+        <v>10974.78</v>
       </c>
     </row>
     <row r="907">
@@ -55778,7 +55778,7 @@
         </is>
       </c>
       <c r="M907" s="2" t="n">
-        <v>7640.56</v>
+        <v>7682.35</v>
       </c>
     </row>
     <row r="908">
@@ -55839,7 +55839,7 @@
         </is>
       </c>
       <c r="M908" s="2" t="n">
-        <v>2281.74</v>
+        <v>2294.22</v>
       </c>
     </row>
     <row r="909">
@@ -55900,7 +55900,7 @@
         </is>
       </c>
       <c r="M909" s="2" t="n">
-        <v>9932.73</v>
+        <v>9987.049999999999</v>
       </c>
     </row>
     <row r="910">
@@ -55961,7 +55961,7 @@
         </is>
       </c>
       <c r="M910" s="2" t="n">
-        <v>9773.93</v>
+        <v>9827.379999999999</v>
       </c>
     </row>
     <row r="911">
@@ -56022,7 +56022,7 @@
         </is>
       </c>
       <c r="M911" s="2" t="n">
-        <v>65490.53</v>
+        <v>65848.67999999999</v>
       </c>
     </row>
     <row r="912">
@@ -56083,7 +56083,7 @@
         </is>
       </c>
       <c r="M912" s="2" t="n">
-        <v>21830.18</v>
+        <v>21949.56</v>
       </c>
     </row>
     <row r="913">
@@ -56144,7 +56144,7 @@
         </is>
       </c>
       <c r="M913" s="2" t="n">
-        <v>19647.16</v>
+        <v>19754.6</v>
       </c>
     </row>
     <row r="914">
@@ -56205,7 +56205,7 @@
         </is>
       </c>
       <c r="M914" s="2" t="n">
-        <v>15062.82</v>
+        <v>15145.2</v>
       </c>
     </row>
     <row r="915">
@@ -56266,7 +56266,7 @@
         </is>
       </c>
       <c r="M915" s="2" t="n">
-        <v>2859.75</v>
+        <v>2875.39</v>
       </c>
     </row>
     <row r="916">
@@ -56327,7 +56327,7 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>2292.17</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="917">
@@ -56388,7 +56388,7 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="918">
@@ -56449,7 +56449,7 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>63174.57</v>
+        <v>63520.06</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/dic-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27393,7 +27393,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27515,7 +27515,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30565,7 +30565,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32090,7 +32090,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32700,7 +32700,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33005,7 +33005,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35994,7 +35994,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38434,7 +38434,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38800,7 +38800,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39227,7 +39227,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39959,7 +39959,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -41179,7 +41179,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41240,7 +41240,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41301,7 +41301,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41728,7 +41728,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41911,7 +41911,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42887,7 +42887,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42948,7 +42948,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -44351,7 +44351,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44656,7 +44656,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -45327,7 +45327,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45449,7 +45449,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45754,7 +45754,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45998,7 +45998,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46120,7 +46120,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46242,7 +46242,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46303,7 +46303,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46913,7 +46913,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -46974,7 +46974,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47401,7 +47401,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47645,7 +47645,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -48499,7 +48499,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -48743,7 +48743,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -49231,7 +49231,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49719,7 +49719,7 @@
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -50146,7 +50146,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -50329,7 +50329,7 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
@@ -50390,7 +50390,7 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
@@ -51366,7 +51366,7 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -51427,7 +51427,7 @@
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -52647,7 +52647,7 @@
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -53257,7 +53257,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -53379,7 +53379,7 @@
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
@@ -53989,7 +53989,7 @@
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
@@ -54050,7 +54050,7 @@
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
@@ -54233,7 +54233,7 @@
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I882" t="inlineStr">
@@ -54355,7 +54355,7 @@
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -54416,7 +54416,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -54538,7 +54538,7 @@
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
@@ -54599,7 +54599,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -54660,7 +54660,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -54782,7 +54782,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -55026,7 +55026,7 @@
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -55453,7 +55453,7 @@
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -55819,7 +55819,7 @@
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -56124,7 +56124,7 @@
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/dic-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/dic-2025.xlsx
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLECO DEPARTAMENTO</t>
+          <t>I MUNICIPALIDAD DE QUILLECO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Libertador Gral. Bernardo O´higgins</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales VII Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE EDUCACION - CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Salud</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Pinto Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>PREDIOS FISCALES IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Metro Regional de Valparaíso S.A.</t>
+          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Salud</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16286,12 +16286,12 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERPLAC I Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERPLAC X REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL CLUB DE LA REINA SOCIAL DEPO</t>
+          <t>CORPORACION MUNICIPAL CLUB DE LA REINA SOCIAL DEPORTIVO Y RECREACIONAL</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Corporación del Deporte e Inclusión Social de la I</t>
+          <t>Corporación del Deporte e Inclusión Social de la Ilustre Municipalidad de Cerro Navia</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>PROGRAMA DE VIALIDAD Y TRANSPORTE URBANO SECTRA</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20922,7 +20922,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22081,7 +22081,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION IV REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24338,12 +24338,12 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LLANQUIHUE-DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -26961,7 +26961,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>SEREMI DESARROLLO SOCIAL REGION DE ÑUBLE</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27388,7 +27388,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Salud</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -27510,7 +27510,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -29035,7 +29035,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -29279,7 +29279,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -30804,7 +30804,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -31719,7 +31719,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -31841,7 +31841,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>SEREMI IX</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>SEREMI IX</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -32268,7 +32268,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -32512,7 +32512,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>Regional Min.Bs.Nac. XIV Región Los Rios</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -32756,7 +32756,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -32822,7 +32822,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32878,7 +32878,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>SERPLAC III Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -33305,7 +33305,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -33549,7 +33549,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -33610,7 +33610,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Municipalidad de Yerbas Buenas-Depto. Salud</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -33976,7 +33976,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -34037,7 +34037,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -34098,7 +34098,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -34464,7 +34464,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Llanquihue</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -35379,7 +35379,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>Secretaría Ministerial de Educación - RM</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -35684,7 +35684,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>Serplac IX Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -35806,7 +35806,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -35928,7 +35928,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -37026,7 +37026,7 @@
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -38124,7 +38124,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -38251,7 +38251,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38490,7 +38490,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -38551,7 +38551,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -39161,7 +39161,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39344,7 +39344,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -39466,7 +39466,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>SEREMI de Educación Arica y Parinacota</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -39588,7 +39588,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -39649,7 +39649,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -39954,7 +39954,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -41601,7 +41601,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VI REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -41967,7 +41967,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -42272,7 +42272,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -42455,7 +42455,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>SEREMI ÑUBLE-REGIÓN XVI</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -43126,7 +43126,7 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -43675,7 +43675,7 @@
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -43980,7 +43980,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -44102,7 +44102,7 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -44163,7 +44163,7 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -44651,7 +44651,7 @@
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -44834,7 +44834,7 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Secretaria Ministerial de Educación Región Ñuble</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -45566,7 +45566,7 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -45688,7 +45688,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>SECRETARIA REG MINIST DE BIENES NACIONAL I REGION</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -46054,7 +46054,7 @@
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -46120,7 +46120,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46237,7 +46237,7 @@
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -46298,7 +46298,7 @@
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE PLANIFICACION Y COORD. VIII REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -47701,7 +47701,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -47767,7 +47767,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47828,7 +47828,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -48494,7 +48494,7 @@
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>Ministerio Publico</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -48682,7 +48682,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -48738,7 +48738,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -48860,7 +48860,7 @@
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
@@ -49043,7 +49043,7 @@
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
@@ -49409,7 +49409,7 @@
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
@@ -49531,7 +49531,7 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
@@ -49714,7 +49714,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
@@ -49958,7 +49958,7 @@
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -50314,7 +50314,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F818" t="inlineStr">
@@ -50385,7 +50385,7 @@
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL BIENES NACIONALES VI REGION</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
@@ -50690,7 +50690,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA SAN ANTONIO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -50751,7 +50751,7 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -50812,7 +50812,7 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
@@ -50878,7 +50878,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -50934,7 +50934,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>SERPLAC X REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -51300,7 +51300,7 @@
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H834" t="inlineStr">
@@ -51483,7 +51483,7 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>Serplac IX Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -51605,7 +51605,7 @@
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales X Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
@@ -52398,7 +52398,7 @@
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
@@ -52459,7 +52459,7 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
@@ -52571,7 +52571,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
@@ -52581,7 +52581,7 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
@@ -53181,7 +53181,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
@@ -53191,7 +53191,7 @@
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
@@ -53313,7 +53313,7 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>SERPLAC V REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
@@ -53679,7 +53679,7 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>DELEGACION PRESIDENCIAL PROVINCIAL DE LOS ANDES</t>
+          <t>GOBERNACION PROVINCIAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H873" t="inlineStr">
@@ -54106,7 +54106,7 @@
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PESCA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
@@ -54289,7 +54289,7 @@
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
@@ -54594,7 +54594,7 @@
       </c>
       <c r="G888" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H888" t="inlineStr">
@@ -54716,7 +54716,7 @@
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
@@ -54777,7 +54777,7 @@
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
@@ -54838,7 +54838,7 @@
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
@@ -54899,7 +54899,7 @@
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
@@ -54960,7 +54960,7 @@
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
@@ -55204,7 +55204,7 @@
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
@@ -55560,7 +55560,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
@@ -55631,7 +55631,7 @@
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H905" t="inlineStr">
@@ -55804,7 +55804,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F908" t="inlineStr">
@@ -56180,7 +56180,7 @@
       </c>
       <c r="G914" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H914" t="inlineStr">
@@ -56302,7 +56302,7 @@
       </c>
       <c r="G916" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H916" t="inlineStr">
@@ -56363,7 +56363,7 @@
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H917" t="inlineStr">
